--- a/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-05-2026.xlsx
+++ b/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-05-2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F108F59F-8405-43D8-B024-6B168073D38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD216EF-9DD8-4114-8E46-514FD5C74EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng tính CK" sheetId="1" r:id="rId1"/>
@@ -816,6 +816,24 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1001,47 +1019,29 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1528,74 +1528,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="85"/>
-      <c r="B1" s="86"/>
-      <c r="C1" s="93" t="s">
+      <c r="A1" s="91"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="85"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="90" t="s">
+      <c r="A2" s="91"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="96" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="98"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="85"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="98" t="s">
+      <c r="A3" s="91"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="100"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="106"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="85"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="87" t="s">
+      <c r="A4" s="91"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="89"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="95"/>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65"/>
       <c r="B6" s="65"/>
       <c r="C6" s="65"/>
       <c r="D6" s="66"/>
-      <c r="E6" s="95" t="str">
+      <c r="E6" s="101" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 30 tháng 05 năm 2026</v>
       </c>
-      <c r="F6" s="95"/>
+      <c r="F6" s="101"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="100" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
       <c r="F7" s="28"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1637,67 +1637,67 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="145">
+      <c r="A11" s="80">
         <v>1</v>
       </c>
-      <c r="B11" s="145" t="s">
+      <c r="B11" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="145">
+      <c r="C11" s="80">
         <v>290</v>
       </c>
-      <c r="D11" s="146">
+      <c r="D11" s="81">
         <v>6000</v>
       </c>
-      <c r="E11" s="146">
+      <c r="E11" s="81">
         <f>SUM(C11*D11)</f>
         <v>1740000</v>
       </c>
-      <c r="F11" s="145" t="s">
+      <c r="F11" s="80" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="145">
+      <c r="A12" s="80">
         <v>2</v>
       </c>
-      <c r="B12" s="145" t="s">
+      <c r="B12" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="145">
+      <c r="C12" s="80">
         <v>6</v>
       </c>
-      <c r="D12" s="146">
+      <c r="D12" s="81">
         <v>6000</v>
       </c>
-      <c r="E12" s="146">
+      <c r="E12" s="81">
         <f>SUM(C12*D12)</f>
         <v>36000</v>
       </c>
-      <c r="F12" s="147" t="s">
+      <c r="F12" s="82" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="80" t="s">
+      <c r="A13" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="81"/>
+      <c r="B13" s="87"/>
       <c r="C13" s="50">
-        <f>SUM(C12:C12)</f>
-        <v>6</v>
+        <f>SUM(C11:C12)</f>
+        <v>296</v>
       </c>
       <c r="D13" s="51"/>
       <c r="E13" s="46"/>
       <c r="F13" s="46"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="82" t="s">
+      <c r="A14" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="82"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="82"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="49">
         <f>SUM(E11:E12)</f>
         <v>1776000</v>
@@ -1721,33 +1721,33 @@
       <c r="F16" s="28"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="83"/>
+      <c r="B17" s="89"/>
       <c r="C17" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="83" t="s">
+      <c r="D17" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="83"/>
+      <c r="E17" s="89"/>
       <c r="F17" s="9" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="84" t="s">
+      <c r="A18" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="84"/>
+      <c r="B18" s="90"/>
       <c r="C18" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="84" t="s">
+      <c r="D18" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="84"/>
+      <c r="E18" s="90"/>
       <c r="F18" s="27" t="s">
         <v>7</v>
       </c>
@@ -1785,17 +1785,17 @@
       <c r="F22" s="22"/>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="83" t="s">
+      <c r="A23" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="83"/>
+      <c r="B23" s="89"/>
       <c r="C23" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="83" t="s">
+      <c r="D23" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="83"/>
+      <c r="E23" s="89"/>
       <c r="F23" s="9" t="s">
         <v>9</v>
       </c>
@@ -1882,64 +1882,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="108"/>
-      <c r="B1" s="109"/>
-      <c r="C1" s="110" t="s">
+      <c r="A1" s="114"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="116" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="108"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="119" t="s">
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="121"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="127"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="108"/>
-      <c r="B3" s="109"/>
-      <c r="C3" s="98" t="s">
+      <c r="A3" s="114"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="100"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="106"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="108"/>
-      <c r="B4" s="109"/>
-      <c r="C4" s="87" t="s">
+      <c r="A4" s="114"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="89"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="95"/>
     </row>
     <row r="5" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="112"/>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="114"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="120"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="70"/>
@@ -1988,10 +1988,10 @@
       <c r="H9" s="28"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="115" t="s">
+      <c r="A10" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="116"/>
+      <c r="B10" s="122"/>
       <c r="C10" s="48">
         <f>'Bảng tính CK'!E14</f>
         <v>1776000</v>
@@ -2003,10 +2003,10 @@
       <c r="H10" s="28"/>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="101" t="s">
+      <c r="A11" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="102"/>
+      <c r="B11" s="108"/>
       <c r="C11" s="48">
         <v>3</v>
       </c>
@@ -2017,10 +2017,10 @@
       <c r="H11" s="28"/>
     </row>
     <row r="12" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="117" t="s">
+      <c r="A12" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="118"/>
+      <c r="B12" s="124"/>
       <c r="C12" s="46">
         <v>0</v>
       </c>
@@ -2031,10 +2031,10 @@
       <c r="H12" s="28"/>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="106" t="s">
+      <c r="A13" s="112" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="107"/>
+      <c r="B13" s="113"/>
       <c r="C13" s="46">
         <f>COUNTIFS(C16:C20, "&gt;=2.5",C16:C20,"&lt;7")</f>
         <v>0</v>
@@ -2091,7 +2091,7 @@
       <c r="C16" s="47">
         <v>0</v>
       </c>
-      <c r="D16" s="155">
+      <c r="D16" s="84">
         <v>1</v>
       </c>
       <c r="E16" s="48">
@@ -2119,7 +2119,7 @@
       <c r="C17" s="47">
         <v>1</v>
       </c>
-      <c r="D17" s="155">
+      <c r="D17" s="84">
         <v>1</v>
       </c>
       <c r="E17" s="48">
@@ -2147,7 +2147,7 @@
       <c r="C18" s="47">
         <v>0.5</v>
       </c>
-      <c r="D18" s="155">
+      <c r="D18" s="84">
         <v>1</v>
       </c>
       <c r="E18" s="48">
@@ -2166,12 +2166,12 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="103" t="s">
+      <c r="A19" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="104"/>
-      <c r="C19" s="105"/>
-      <c r="D19" s="156">
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="85">
         <f>SUM(D16:D18)</f>
         <v>3</v>
       </c>
@@ -2203,11 +2203,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="80" t="s">
+      <c r="A21" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="122"/>
-      <c r="C21" s="81"/>
+      <c r="B21" s="128"/>
+      <c r="C21" s="87"/>
       <c r="D21" s="33"/>
       <c r="E21" s="49">
         <f>SUM(E16:E18)</f>
@@ -2250,40 +2250,40 @@
       <c r="H23" s="57"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="123" t="s">
+      <c r="A24" s="129" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="123"/>
-      <c r="C24" s="123" t="s">
+      <c r="B24" s="129"/>
+      <c r="C24" s="129" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="123"/>
-      <c r="E24" s="124" t="s">
+      <c r="D24" s="129"/>
+      <c r="E24" s="130" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="124"/>
-      <c r="G24" s="123" t="s">
+      <c r="F24" s="130"/>
+      <c r="G24" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="H24" s="123"/>
+      <c r="H24" s="129"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="84" t="s">
+      <c r="A25" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="84"/>
-      <c r="C25" s="84" t="s">
+      <c r="B25" s="90"/>
+      <c r="C25" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="84"/>
-      <c r="E25" s="125" t="s">
+      <c r="D25" s="90"/>
+      <c r="E25" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="125"/>
-      <c r="G25" s="84" t="s">
+      <c r="F25" s="131"/>
+      <c r="G25" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="84"/>
+      <c r="H25" s="90"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="56"/>
@@ -2326,22 +2326,22 @@
       <c r="H29" s="57"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="123" t="s">
+      <c r="A30" s="129" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="123"/>
-      <c r="C30" s="123" t="s">
+      <c r="B30" s="129"/>
+      <c r="C30" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="123"/>
-      <c r="E30" s="124" t="s">
+      <c r="D30" s="129"/>
+      <c r="E30" s="130" t="s">
         <v>35</v>
       </c>
-      <c r="F30" s="124"/>
-      <c r="G30" s="123" t="s">
+      <c r="F30" s="130"/>
+      <c r="G30" s="129" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="123"/>
+      <c r="H30" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -2398,55 +2398,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="134"/>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="135" t="s">
+      <c r="A1" s="140"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="141" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="141" t="s">
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="147" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="142"/>
+      <c r="H1" s="148"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="134"/>
-      <c r="B2" s="134"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="141" t="s">
+      <c r="A2" s="140"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="142"/>
+      <c r="H2" s="148"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="134"/>
-      <c r="B3" s="134"/>
-      <c r="C3" s="134"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="141" t="s">
+      <c r="A3" s="140"/>
+      <c r="B3" s="140"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="147" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="142"/>
+      <c r="H3" s="148"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="133" t="str">
+      <c r="A4" s="139" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 30 tháng 05 năm 2026</v>
       </c>
-      <c r="B4" s="133"/>
-      <c r="C4" s="133"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="133"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="139"/>
+      <c r="H4" s="139"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
@@ -2483,27 +2483,27 @@
       <c r="H7" s="18"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="127" t="s">
+      <c r="A8" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="127" t="s">
+      <c r="B8" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="129" t="s">
+      <c r="C8" s="135" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="130"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="131"/>
-      <c r="G8" s="132" t="s">
+      <c r="D8" s="136"/>
+      <c r="E8" s="136"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="138" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="132"/>
+      <c r="H8" s="138"/>
       <c r="I8" s="55"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="128"/>
-      <c r="B9" s="128"/>
+      <c r="A9" s="134"/>
+      <c r="B9" s="134"/>
       <c r="C9" s="37" t="s">
         <v>62</v>
       </c>
@@ -2516,8 +2516,8 @@
       <c r="F9" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="132"/>
-      <c r="H9" s="132"/>
+      <c r="G9" s="138"/>
+      <c r="H9" s="138"/>
       <c r="I9" s="55"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2540,10 +2540,10 @@
         <f>D10-E10</f>
         <v>2</v>
       </c>
-      <c r="G10" s="126" t="s">
+      <c r="G10" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="126"/>
+      <c r="H10" s="132"/>
       <c r="I10" s="55"/>
     </row>
     <row r="11" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2566,10 +2566,10 @@
         <f>SUM(D11-E11)</f>
         <v>203</v>
       </c>
-      <c r="G11" s="148" t="s">
+      <c r="G11" s="151" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="149"/>
+      <c r="H11" s="152"/>
       <c r="I11" s="55"/>
     </row>
     <row r="12" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2592,10 +2592,10 @@
         <f>SUM(D12-E12)</f>
         <v>3000</v>
       </c>
-      <c r="G12" s="148" t="s">
+      <c r="G12" s="151" t="s">
         <v>74</v>
       </c>
-      <c r="H12" s="149"/>
+      <c r="H12" s="152"/>
       <c r="I12" s="55"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -2618,10 +2618,10 @@
         <f>D13-E13</f>
         <v>2</v>
       </c>
-      <c r="G13" s="126" t="s">
+      <c r="G13" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="126"/>
+      <c r="H13" s="132"/>
       <c r="I13" s="55"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -2644,10 +2644,10 @@
         <f t="shared" ref="F14" si="0">D14</f>
         <v>178</v>
       </c>
-      <c r="G14" s="126" t="s">
+      <c r="G14" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="126"/>
+      <c r="H14" s="132"/>
       <c r="I14" s="55"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -2670,10 +2670,10 @@
         <f>D15-E15</f>
         <v>52</v>
       </c>
-      <c r="G15" s="126" t="s">
+      <c r="G15" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="126"/>
+      <c r="H15" s="132"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="79">
@@ -2695,10 +2695,10 @@
         <f>D16-E16</f>
         <v>22</v>
       </c>
-      <c r="G16" s="126" t="s">
+      <c r="G16" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="126"/>
+      <c r="H16" s="132"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="79">
@@ -2720,10 +2720,10 @@
         <f>D17-E17</f>
         <v>2</v>
       </c>
-      <c r="G17" s="126" t="s">
+      <c r="G17" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="126"/>
+      <c r="H17" s="132"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="79">
@@ -2744,10 +2744,10 @@
       <c r="F18" s="41">
         <v>3</v>
       </c>
-      <c r="G18" s="126" t="s">
+      <c r="G18" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="126"/>
+      <c r="H18" s="132"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="79">
@@ -2758,40 +2758,41 @@
       </c>
       <c r="C19" s="39"/>
       <c r="D19" s="39">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="E19" s="39">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="F19" s="41">
-        <v>0</v>
-      </c>
-      <c r="G19" s="126"/>
-      <c r="H19" s="126"/>
+        <f>SUM(D19-E19)</f>
+        <v>3</v>
+      </c>
+      <c r="G19" s="132"/>
+      <c r="H19" s="132"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="150" t="s">
+      <c r="A20" s="155" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="151"/>
-      <c r="C20" s="152">
+      <c r="B20" s="156"/>
+      <c r="C20" s="83">
         <f>SUM(C10:C19)</f>
         <v>5960</v>
       </c>
-      <c r="D20" s="152">
+      <c r="D20" s="83">
         <f>SUM(D10:D19)</f>
-        <v>3843</v>
-      </c>
-      <c r="E20" s="152">
+        <v>3763</v>
+      </c>
+      <c r="E20" s="83">
         <f>SUM(E10:E19)</f>
-        <v>379</v>
-      </c>
-      <c r="F20" s="152">
+        <v>296</v>
+      </c>
+      <c r="F20" s="83">
         <f>SUM(F10:F19)</f>
-        <v>3464</v>
-      </c>
-      <c r="G20" s="153"/>
-      <c r="H20" s="154"/>
+        <v>3467</v>
+      </c>
+      <c r="G20" s="149"/>
+      <c r="H20" s="150"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="18"/>
@@ -2804,40 +2805,40 @@
       <c r="H21" s="18"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="144" t="s">
+      <c r="A22" s="154" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="144"/>
-      <c r="C22" s="144" t="s">
+      <c r="B22" s="154"/>
+      <c r="C22" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="144"/>
-      <c r="E22" s="144" t="s">
+      <c r="D22" s="154"/>
+      <c r="E22" s="154" t="s">
         <v>59</v>
       </c>
-      <c r="F22" s="144"/>
-      <c r="G22" s="83" t="s">
+      <c r="F22" s="154"/>
+      <c r="G22" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="H22" s="83"/>
+      <c r="H22" s="89"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="84" t="s">
+      <c r="A23" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="84"/>
-      <c r="C23" s="84" t="s">
+      <c r="B23" s="90"/>
+      <c r="C23" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="84"/>
-      <c r="E23" s="84" t="s">
+      <c r="D23" s="90"/>
+      <c r="E23" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="F23" s="84"/>
-      <c r="G23" s="84" t="s">
+      <c r="F23" s="90"/>
+      <c r="G23" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="84"/>
+      <c r="H23" s="90"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="32"/>
@@ -2880,22 +2881,22 @@
       <c r="H27" s="43"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="143" t="s">
+      <c r="A28" s="153" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="143"/>
-      <c r="C28" s="143" t="s">
+      <c r="B28" s="153"/>
+      <c r="C28" s="153" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="143"/>
-      <c r="E28" s="143" t="s">
+      <c r="D28" s="153"/>
+      <c r="E28" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="143"/>
-      <c r="G28" s="143" t="s">
+      <c r="F28" s="153"/>
+      <c r="G28" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="H28" s="143"/>
+      <c r="H28" s="153"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="35"/>
